--- a/cases/the-trailer-return/published/The Trailer Return - Data.xlsx
+++ b/cases/the-trailer-return/published/The Trailer Return - Data.xlsx
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>$1.1391 / mi (computed: $5.967 ÷ 5.2392)</t>
+          <t>$1.1389 / mi (computed: $5.967 ÷ 5.2392)</t>
         </is>
       </c>
     </row>
